--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -227,7 +227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Arial"/>
       <sz val="11"/>
@@ -236,6 +236,10 @@
       <name val="Arial"/>
       <sz val="11"/>
       <color indexed="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -310,7 +314,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -331,7 +335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData>
     <row r="1" spans="8:8">
@@ -507,7 +511,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData>
     <row r="1" spans="8:8">
@@ -521,14 +525,25 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="8:8">
-      <c r="A2" t="s">
+    <row r="3" spans="8:8">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="8:8">
+      <c r="A4" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B4" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" t="s">
         <v>67</v>
       </c>
     </row>
@@ -540,7 +555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="16.25" defaultColWidth="10"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
